--- a/469/food/2026-02-24-sm.xlsx
+++ b/469/food/2026-02-24-sm.xlsx
@@ -857,7 +857,7 @@
       </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>2026-02-24</t>
         </is>
       </c>
     </row>
